--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_357_Andaman_Nicobar_Isl_India.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_357_Andaman_Nicobar_Isl_India.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rcf59051fb5ec4c4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R08bc5e1a62784a4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rcb180a3879494d93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Re594dd2de9634a42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R736c803e777e49ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R348aa85b82634270"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R7bde313ea9554d39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rada863f9923b4c2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R2cd7f9794fe745e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R08c7d37cc41f41f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R20c5b00a3a8341be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R0c1a8a36d5574366"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ357CommercialTable" displayName="EEZ357CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ357CommercialTable" displayName="EEZ357CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ357FunctionalTable" displayName="EEZ357FunctionalTable" ref="A1:O18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O18"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ357FunctionalTable" displayName="EEZ357FunctionalTable" ref="A1:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E18"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ357ValidationTable" displayName="EEZ357ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ357ValidationTable" displayName="EEZ357ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6724,7 +6678,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cba514ee08f4558"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree1d39e9d39e4fa2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6734,20 +6688,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6755,552 +6699,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>3635.5065243312</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2404298874096065</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>173.95218466042036</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>3635.5065243312</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>176.81978283348693</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$91,A2,'Species'!$U$2:$U$91))</x:f>
-        <x:v>642829.4741219677</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2404298874096065</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>173.95218466042036</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>632404.302254624</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>10425.171867343714</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0164849793560484</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.016484979356048472</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>792.4296009395</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.2911402796596625</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>195.49708208205416</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>792.4296009395</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>195.9849815993776</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$91,A3,'Species'!$U$2:$U$91))</x:f>
-        <x:v>155304.30075893004</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.2911402796596625</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>195.49708208205416</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>154917.67473911887</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>386.6260198111704</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.002495686954134</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0024956869541338522</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>10.2606940146</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.57</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>371.5352290971724</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>10.2606940146</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$91,A4,'Species'!$U$2:$U$91))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3812.209301410397</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.57</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>3812.209301410397</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>5744.618179729201</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.8403586866334254</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>69.24025946327622</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>5744.618179729201</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>95.6899643328882</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$91,A5,'Species'!$U$2:$U$91))</x:f>
-        <x:v>549702.3087243483</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.8403586866334254</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>69.24025946327622</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>397758.85328190343</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>151943.4554424449</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.381998927714019</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.38199892771401894</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>228.5106950954</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.1731714455667355</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>14.899491458817248</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>228.5106950954</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>15.021714763279485</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$91,A6,'Species'!$U$2:$U$91))</x:f>
-        <x:v>3432.622482081827</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.1731714455667355</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>14.899491458817248</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>3404.693149822305</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>27.929332259522198</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.008203186316799</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.00820318631679917</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>13272.542730127603</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.249069591544346</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>177.4473800594749</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>13272.542730127603</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>195.9688389202344</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$91,A7,'Species'!$U$2:$U$91))</x:f>
-        <x:v>2601004.788342304</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.249069591544346</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>177.4473800594749</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2355177.9341885736</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>245826.85415373044</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1043771897593058</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.10437718975930574</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>25204.1945691117</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.9363730035567412</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>863.720054633119</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>25204.1945691117</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1394.2046923877124</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$91,A8,'Species'!$U$2:$U$91))</x:f>
-        <x:v>35139806.33610843</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.9363730035567412</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>863.720054633119</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>21769368.31021692</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>13370438.025891513</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.6141858521276626</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.6141858521276626</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>4577.99240378</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.168836944565506</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1475.1525847110238</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>4577.99240378</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1773.2403535178714</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$91,A9,'Species'!$U$2:$U$91))</x:f>
-        <x:v>8117880.868480978</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.168836944565506</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1475.1525847110238</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>6753237.3272235</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1364643.5412574774</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2020724987342526</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.20207249873425248</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>7837.2555985278</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.445604973405622</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2790.0049474960965</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>7837.2555985278</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2836.5176332703386</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$91,A10,'Species'!$U$2:$U$91))</x:f>
-        <x:v>22230513.70167079</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.445604973405622</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2790.0049474960965</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>21865981.894684043</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>364531.80698674545</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0166711839762095</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.01667118397620958</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cacec30cf7a4919"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18c55b6614e04496"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7310,20 +6895,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7331,984 +6906,345 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>83.58197426059999</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.81</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>645.6542290346556</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>83.58197426059999</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>645.6542290346556</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$91,A2,'Species'!$U$2:$U$91))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>53965.055152422115</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.81</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>645.6542290346556</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>53965.055152422115</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>223.6447396452</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.093500570910284</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>124.02252554801217</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>223.6447396452</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>714.380362026478</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$91,A3,'Species'!$U$2:$U$91))</x:f>
-        <x:v>159767.4100730554</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.093500570910284</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>124.02252554801217</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>27736.985436325347</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>132030.42463673005</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>5.760085588241982</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>4.760085588241983</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>334.4164216379</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.199993483603244</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1584.8694120176424</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>334.4164216379</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1757.2359212042466</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$91,A4,'Species'!$U$2:$U$91))</x:f>
-        <x:v>587648.5487427029</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.199993483603244</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1584.8694120176424</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>530006.3575303025</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>57642.191212400445</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1087575467603799</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.1087575467603798</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>12113.206928074802</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.469433521434107</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2947.3622818001486</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>12113.206928074802</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2971.542465048713</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$91,A5,'Species'!$U$2:$U$91))</x:f>
-        <x:v>35994908.774696544</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.469433521434107</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2947.3622818001486</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>35702009.21144792</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>292899.5632486269</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0082040078336743</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.008204007833674193</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>30.5991393089</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>3162.2776601683795</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>30.5991393089</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$91,A6,'Species'!$U$2:$U$91))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>96762.97465691458</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>96762.97465691458</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>4577.99240378</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.168836944565506</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1475.1525847110238</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>4577.99240378</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1773.2403535178714</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$91,A7,'Species'!$U$2:$U$91))</x:f>
-        <x:v>8117880.868480978</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.168836944565506</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1475.1525847110238</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>6753237.3272235</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1364643.5412574774</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.2020724987342526</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.20207249873425248</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1758.3192836087</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.228907735799188</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>169.39778830980512</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1758.3192836087</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>177.5428841016321</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$91,A8,'Species'!$U$2:$U$91))</x:f>
-        <x:v>312177.0767834042</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.228907735799188</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>169.39778830980512</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>297855.39778579475</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>14321.678997609473</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0480826572359419</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.04808265723594182</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>12886.072996975001</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.2815718388448682</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>191.23696331674967</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>12886.072996975001</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>198.5341181821241</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$91,A9,'Species'!$U$2:$U$91))</x:f>
-        <x:v>2558325.139284913</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.2815718388448682</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>191.23696331674967</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2464293.4690194665</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>94031.67026544642</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0381576591617805</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.03815765916178047</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>8742.24449263</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.016321261723978</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1038.2961932017329</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>8742.24449263</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1318.8585801973372</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$91,A10,'Species'!$U$2:$U$91))</x:f>
-        <x:v>11529784.159287993</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.016321261723978</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1038.2961932017329</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>9077039.176736543</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>2452744.98255145</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.2702142113518213</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.2702142113518213</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>9081.3947571822</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.8088765515680993</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>643.9861860885436</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>9081.3947571822</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>957.5852577903153</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$91,A11,'Species'!$U$2:$U$91))</x:f>
-        <x:v>8696209.739651933</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.8088765515680993</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>643.9861860885436</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>5848292.77404226</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2847916.9656096734</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.4869655257770606</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.4869655257770606</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>562.9198564654</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.070296911616516</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>11.757010650437762</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>562.9198564654</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>12.03850604655009</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$91,A12,'Species'!$U$2:$U$91))</x:f>
-        <x:v>6776.7140957818265</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.070296911616516</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>11.757010650437762</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>6618.254747806604</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>158.45934797522204</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0239427695084928</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.023942769508492855</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>792.4296009395</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.2911402796596625</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>195.49708208205416</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>792.4296009395</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>195.9849815993776</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$91,A13,'Species'!$U$2:$U$91))</x:f>
-        <x:v>155304.30075893004</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.2911402796596625</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>195.49708208205416</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>154917.67473911887</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>386.6260198111704</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.002495686954134</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.0024956869541338522</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>640.2805578331</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.1851600372457307</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>153.16517704241113</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>640.2805578331</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>156.38062862101225</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$91,A14,'Species'!$U$2:$U$91))</x:f>
-        <x:v>100127.47612775257</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.1851600372457307</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>153.16517704241113</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>98068.68499732052</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>2058.791130432044</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0209933592001188</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.020993359200118727</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>46.06570390230001</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.6142080498234463</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>411.3467305594104</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>46.06570390230001</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>411.95803473573886</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$91,A15,'Species'!$U$2:$U$91))</x:f>
-        <x:v>18977.13684830997</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.6142080498234463</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>411.3467305594104</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>18948.97669112898</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>28.16015718098788</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0014861043759777</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.0014861043759777878</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>9308.4117261482</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.9853734115060004</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>96.68818580949623</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>9308.4117261482</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>112.77273129063151</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$91,A16,'Species'!$U$2:$U$91))</x:f>
-        <x:v>1049735.0143354745</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.9853734115060004</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>96.68818580949623</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>900013.4425691108</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>149721.5717663637</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.1663548172558176</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.16635481725581758</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>111.4697192506</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.28</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>19.054607179632463</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>111.4697192506</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>19.054607179632463</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$91,A17,'Species'!$U$2:$U$91))</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>2124.0117127440976</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.28</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>19.054607179632463</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
-        <x:v>2124.0117127440976</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>10.2606940146</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.57</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>371.5352290971724</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>10.2606940146</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$91,A18,'Species'!$U$2:$U$91))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>3812.209301410397</x:v>
       </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.57</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>3812.209301410397</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G18">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O18">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00f10cbec3be413b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9c9685d7ca443d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8483,7 +7419,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8582,7 +7518,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>69444286.60999125</x:v>
+        <x:v>53936063.19903991</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8596,7 +7532,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>69444286.60999125</x:v>
+        <x:v>62035701.98379009</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8610,7 +7546,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-15508223.410951339</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8624,7 +7560,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-7408584.62620116</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8635,9 +7571,9 @@
         <x:v>EEZ_357</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8649,47 +7585,19 @@
         <x:v>EEZ_357</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_357</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_357</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra03bf99d74564362"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R434dc755d0ad47cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8736,7 +7644,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
